--- a/content/작품/작품리스트.xlsx
+++ b/content/작품/작품리스트.xlsx
@@ -1,116 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
-  <si>
-    <t>제목(국문)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제목(영문)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제작연도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>재료(국문)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>재료(영문)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사이즈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>캔버스 위에 아크릴릭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Acrylic on canvas</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100 x 100 cm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>참조 코드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Test2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1020 x 1020 cm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="000"/>
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -125,39 +64,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -199,7 +118,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -234,7 +153,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -301,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -436,98 +351,80 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="22.375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="22.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="19.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="23.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="19.5" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1"/>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2025</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="4">
-        <v>2</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>제목(국문)</v>
+      </c>
+      <c r="B1" t="str">
+        <v>제목(영문)</v>
+      </c>
+      <c r="C1" t="str">
+        <v>제작연도</v>
+      </c>
+      <c r="D1" t="str">
+        <v>재료(국문)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>재료(영문)</v>
+      </c>
+      <c r="F1" t="str">
+        <v>사이즈</v>
+      </c>
+      <c r="G1" t="str">
+        <v>참조 코드</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/content/작품/작품리스트.xlsx
+++ b/content/작품/작품리스트.xlsx
@@ -1,55 +1,116 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="122211"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+  <si>
+    <t>제목(국문)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제목(영문)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제작연도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재료(국문)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재료(영문)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사이즈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캔버스 위에 아크릴릭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Acrylic on canvas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100 x 100 cm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>참조 코드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1020 x 1020 cm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="176" formatCode="000"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,19 +125,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -118,7 +199,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -153,7 +234,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -220,16 +301,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,80 +436,98 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="22.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="19.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="23.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.5" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>제목(국문)</v>
-      </c>
-      <c r="B1" t="str">
-        <v>제목(영문)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>제작연도</v>
-      </c>
-      <c r="D1" t="str">
-        <v>재료(국문)</v>
-      </c>
-      <c r="E1" t="str">
-        <v>재료(영문)</v>
-      </c>
-      <c r="F1" t="str">
-        <v>사이즈</v>
-      </c>
-      <c r="G1" t="str">
-        <v>참조 코드</v>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2025</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
-  </ignoredErrors>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/content/작품/작품리스트.xlsx
+++ b/content/작품/작품리스트.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="130">
   <si>
     <t>제목(국문)</t>
   </si>
@@ -71,6 +71,336 @@
   </si>
   <si>
     <t>1-03</t>
+  </si>
+  <si>
+    <t>53×45.5cm</t>
+  </si>
+  <si>
+    <t>1-04</t>
+  </si>
+  <si>
+    <t>유리잔</t>
+  </si>
+  <si>
+    <t>Glass</t>
+  </si>
+  <si>
+    <t>100×72.7cm</t>
+  </si>
+  <si>
+    <t>1-05</t>
+  </si>
+  <si>
+    <t>유리잔 안에 티스푼</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Teaspoon in Glass</t>
+  </si>
+  <si>
+    <t>130.3×97cm</t>
+  </si>
+  <si>
+    <t>1-06</t>
+  </si>
+  <si>
+    <t>화병</t>
+  </si>
+  <si>
+    <t>Vase</t>
+  </si>
+  <si>
+    <t>72.7×90.9cm</t>
+  </si>
+  <si>
+    <t>1-07</t>
+  </si>
+  <si>
+    <t>램프</t>
+  </si>
+  <si>
+    <t>Lamp</t>
+  </si>
+  <si>
+    <t>65.1×90.9cm</t>
+  </si>
+  <si>
+    <t>1-08</t>
+  </si>
+  <si>
+    <t>꺼진 TV</t>
+  </si>
+  <si>
+    <t>TV turned off</t>
+  </si>
+  <si>
+    <t>1-09</t>
+  </si>
+  <si>
+    <t>찻잔 위에 빗물</t>
+  </si>
+  <si>
+    <t>Rain in a Teacup</t>
+  </si>
+  <si>
+    <t>생면천 위에 아크릴릭</t>
+  </si>
+  <si>
+    <t>Acrylic on cotton cloth</t>
+  </si>
+  <si>
+    <t>80.3×65.1cm</t>
+  </si>
+  <si>
+    <t>2-01</t>
+  </si>
+  <si>
+    <t>원</t>
+  </si>
+  <si>
+    <t>Circles</t>
+  </si>
+  <si>
+    <t>72.7×60.6cm</t>
+  </si>
+  <si>
+    <t>2-02</t>
+  </si>
+  <si>
+    <t>무제</t>
+  </si>
+  <si>
+    <t>Untitled</t>
+  </si>
+  <si>
+    <t>65.1×80.3cm</t>
+  </si>
+  <si>
+    <t>2-03</t>
+  </si>
+  <si>
+    <t>85×72 cm</t>
+  </si>
+  <si>
+    <t>2-04</t>
+  </si>
+  <si>
+    <t>100×80.3cm</t>
+  </si>
+  <si>
+    <t>2-05</t>
+  </si>
+  <si>
+    <t>116.8×91cm</t>
+  </si>
+  <si>
+    <t>2-06</t>
+  </si>
+  <si>
+    <t>72×85cm</t>
+  </si>
+  <si>
+    <t>2-07</t>
+  </si>
+  <si>
+    <t>80.3×100cm</t>
+  </si>
+  <si>
+    <t>2-08</t>
+  </si>
+  <si>
+    <t>2-09</t>
+  </si>
+  <si>
+    <t>100×80.3 cm</t>
+  </si>
+  <si>
+    <t>2-10</t>
+  </si>
+  <si>
+    <t>80.3×65.1 cm</t>
+  </si>
+  <si>
+    <t>2-11</t>
+  </si>
+  <si>
+    <t>162.2×103.3cm</t>
+  </si>
+  <si>
+    <t>3-01</t>
+  </si>
+  <si>
+    <t>3-02</t>
+  </si>
+  <si>
+    <t>3-03</t>
+  </si>
+  <si>
+    <t>스도쿠</t>
+  </si>
+  <si>
+    <t>Sdoku</t>
+  </si>
+  <si>
+    <t>80.3×116.8cm</t>
+  </si>
+  <si>
+    <t>3-04</t>
+  </si>
+  <si>
+    <t>3-05</t>
+  </si>
+  <si>
+    <t>무제-고스트 프린트</t>
+  </si>
+  <si>
+    <t>Untitled-Ghost Print</t>
+  </si>
+  <si>
+    <t>모노타입</t>
+  </si>
+  <si>
+    <t>Monotype</t>
+  </si>
+  <si>
+    <t>50×65cm</t>
+  </si>
+  <si>
+    <t>4-01</t>
+  </si>
+  <si>
+    <t>33×43.5cm</t>
+  </si>
+  <si>
+    <t>4-02</t>
+  </si>
+  <si>
+    <t>물수제비</t>
+  </si>
+  <si>
+    <t>Skipping Stones</t>
+  </si>
+  <si>
+    <t>90.9×72.7cm</t>
+  </si>
+  <si>
+    <t>5-01</t>
+  </si>
+  <si>
+    <t>선과 선 사이</t>
+  </si>
+  <si>
+    <t>Between Lines (Mixed Blue)</t>
+  </si>
+  <si>
+    <t>91×116.8cm</t>
+  </si>
+  <si>
+    <t>5-02</t>
+  </si>
+  <si>
+    <t>Between Lines (Ochre)</t>
+  </si>
+  <si>
+    <t>5-03</t>
+  </si>
+  <si>
+    <t>잠영</t>
+  </si>
+  <si>
+    <t>Submerge</t>
+  </si>
+  <si>
+    <t>130.3×193.9cm</t>
+  </si>
+  <si>
+    <t>5-04</t>
+  </si>
+  <si>
+    <t>주행과 주행</t>
+  </si>
+  <si>
+    <t>Drive and Drive</t>
+  </si>
+  <si>
+    <t>90×130.3cm</t>
+  </si>
+  <si>
+    <t>5-05</t>
+  </si>
+  <si>
+    <t>평평한 주행 (좁은 문)</t>
+  </si>
+  <si>
+    <t>Flat Drive (Narrow Door)</t>
+  </si>
+  <si>
+    <t>193.9×130.3cm</t>
+  </si>
+  <si>
+    <t>5-06</t>
+  </si>
+  <si>
+    <t>평평한 주행</t>
+  </si>
+  <si>
+    <t>Flat Drive</t>
+  </si>
+  <si>
+    <t>72.7×72.7cm</t>
+  </si>
+  <si>
+    <t>5-07</t>
+  </si>
+  <si>
+    <t>112.1×145.5cm</t>
+  </si>
+  <si>
+    <t>5-08</t>
+  </si>
+  <si>
+    <t>Between Lines</t>
+  </si>
+  <si>
+    <t>97×162.2cm</t>
+  </si>
+  <si>
+    <t>6-01</t>
+  </si>
+  <si>
+    <t>37.9×45.5cm</t>
+  </si>
+  <si>
+    <t>6-02</t>
+  </si>
+  <si>
+    <t>6-03</t>
+  </si>
+  <si>
+    <t>Between Lines (Flesh Tint)</t>
+  </si>
+  <si>
+    <t>144×110cm</t>
+  </si>
+  <si>
+    <t>7-01</t>
+  </si>
+  <si>
+    <t>집으로</t>
+  </si>
+  <si>
+    <t>On the way home</t>
+  </si>
+  <si>
+    <t>캔버스 위에 모노타입</t>
+  </si>
+  <si>
+    <t>Monotype on canvas</t>
+  </si>
+  <si>
+    <t>16×21cm</t>
+  </si>
+  <si>
+    <t>7-02</t>
   </si>
 </sst>
 </file>
@@ -97,7 +427,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -107,6 +437,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="11"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="12"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="13"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="14"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="15"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -184,7 +544,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -200,10 +560,40 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -234,6 +624,11 @@
       <rgbColor rgb="ff000000"/>
       <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="fffbcaa2"/>
+      <rgbColor rgb="ffa5d5e2"/>
+      <rgbColor rgb="ffdfa7a6"/>
+      <rgbColor rgb="ffcdddac"/>
+      <rgbColor rgb="ffbfb1d0"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1295,7 +1690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="16.5" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="22.3516" style="1" customWidth="1"/>
@@ -1401,58 +1796,873 @@
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
+      <c r="A5" t="s" s="7">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s" s="7">
+        <v>14</v>
+      </c>
+      <c r="C5" s="8">
+        <v>2019</v>
+      </c>
+      <c r="D5" t="s" s="7">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s" s="7">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s" s="7">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s" s="7">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+      <c r="A6" t="s" s="7">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s" s="7">
+        <v>23</v>
+      </c>
+      <c r="C6" s="8">
+        <v>2019</v>
+      </c>
+      <c r="D6" t="s" s="7">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s" s="7">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s" s="7">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s" s="7">
+        <v>25</v>
+      </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
+      <c r="A7" t="s" s="7">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s" s="7">
+        <v>27</v>
+      </c>
+      <c r="C7" s="8">
+        <v>2019</v>
+      </c>
+      <c r="D7" t="s" s="7">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s" s="7">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s" s="7">
+        <v>28</v>
+      </c>
+      <c r="G7" t="s" s="7">
+        <v>29</v>
+      </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
+      <c r="A8" t="s" s="7">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s" s="7">
+        <v>31</v>
+      </c>
+      <c r="C8" s="8">
+        <v>2019</v>
+      </c>
+      <c r="D8" t="s" s="7">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s" s="7">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s" s="7">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s" s="7">
+        <v>33</v>
+      </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="A9" t="s" s="7">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s" s="7">
+        <v>35</v>
+      </c>
+      <c r="C9" s="8">
+        <v>2019</v>
+      </c>
+      <c r="D9" t="s" s="7">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s" s="7">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s" s="7">
+        <v>36</v>
+      </c>
+      <c r="G9" t="s" s="7">
+        <v>37</v>
+      </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="A10" t="s" s="7">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s" s="7">
+        <v>39</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2019</v>
+      </c>
+      <c r="D10" t="s" s="7">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s" s="7">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s" s="7">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" t="s" s="9">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s" s="9">
+        <v>42</v>
+      </c>
+      <c r="C11" s="10">
+        <v>2021</v>
+      </c>
+      <c r="D11" t="s" s="9">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s" s="9">
+        <v>44</v>
+      </c>
+      <c r="F11" t="s" s="9">
+        <v>45</v>
+      </c>
+      <c r="G11" t="s" s="9">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" t="s" s="9">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s" s="9">
+        <v>48</v>
+      </c>
+      <c r="C12" s="10">
+        <v>2021</v>
+      </c>
+      <c r="D12" t="s" s="9">
+        <v>43</v>
+      </c>
+      <c r="E12" t="s" s="9">
+        <v>44</v>
+      </c>
+      <c r="F12" t="s" s="9">
+        <v>49</v>
+      </c>
+      <c r="G12" t="s" s="9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" t="s" s="9">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s" s="9">
+        <v>52</v>
+      </c>
+      <c r="C13" s="10">
+        <v>2021</v>
+      </c>
+      <c r="D13" t="s" s="9">
+        <v>43</v>
+      </c>
+      <c r="E13" t="s" s="9">
+        <v>44</v>
+      </c>
+      <c r="F13" t="s" s="9">
+        <v>53</v>
+      </c>
+      <c r="G13" t="s" s="9">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" t="s" s="9">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s" s="9">
+        <v>52</v>
+      </c>
+      <c r="C14" s="10">
+        <v>2021</v>
+      </c>
+      <c r="D14" t="s" s="9">
+        <v>43</v>
+      </c>
+      <c r="E14" t="s" s="9">
+        <v>44</v>
+      </c>
+      <c r="F14" t="s" s="9">
+        <v>55</v>
+      </c>
+      <c r="G14" t="s" s="9">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" t="s" s="9">
+        <v>51</v>
+      </c>
+      <c r="B15" t="s" s="9">
+        <v>52</v>
+      </c>
+      <c r="C15" s="10">
+        <v>2021</v>
+      </c>
+      <c r="D15" t="s" s="9">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s" s="9">
+        <v>44</v>
+      </c>
+      <c r="F15" t="s" s="9">
+        <v>57</v>
+      </c>
+      <c r="G15" t="s" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" t="s" s="9">
+        <v>51</v>
+      </c>
+      <c r="B16" t="s" s="9">
+        <v>52</v>
+      </c>
+      <c r="C16" s="10">
+        <v>2021</v>
+      </c>
+      <c r="D16" t="s" s="9">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s" s="9">
+        <v>44</v>
+      </c>
+      <c r="F16" t="s" s="9">
+        <v>59</v>
+      </c>
+      <c r="G16" t="s" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" t="s" s="9">
+        <v>51</v>
+      </c>
+      <c r="B17" t="s" s="9">
+        <v>52</v>
+      </c>
+      <c r="C17" s="10">
+        <v>2021</v>
+      </c>
+      <c r="D17" t="s" s="9">
+        <v>43</v>
+      </c>
+      <c r="E17" t="s" s="9">
+        <v>44</v>
+      </c>
+      <c r="F17" t="s" s="9">
+        <v>61</v>
+      </c>
+      <c r="G17" t="s" s="9">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" t="s" s="9">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s" s="9">
+        <v>52</v>
+      </c>
+      <c r="C18" s="10">
+        <v>2021</v>
+      </c>
+      <c r="D18" t="s" s="9">
+        <v>43</v>
+      </c>
+      <c r="E18" t="s" s="9">
+        <v>44</v>
+      </c>
+      <c r="F18" t="s" s="9">
+        <v>63</v>
+      </c>
+      <c r="G18" t="s" s="9">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" t="s" s="9">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s" s="9">
+        <v>52</v>
+      </c>
+      <c r="C19" s="10">
+        <v>2021</v>
+      </c>
+      <c r="D19" t="s" s="9">
+        <v>43</v>
+      </c>
+      <c r="E19" t="s" s="9">
+        <v>44</v>
+      </c>
+      <c r="F19" t="s" s="9">
+        <v>63</v>
+      </c>
+      <c r="G19" t="s" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" t="s" s="9">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s" s="9">
+        <v>52</v>
+      </c>
+      <c r="C20" s="10">
+        <v>2021</v>
+      </c>
+      <c r="D20" t="s" s="9">
+        <v>43</v>
+      </c>
+      <c r="E20" t="s" s="9">
+        <v>44</v>
+      </c>
+      <c r="F20" t="s" s="9">
+        <v>66</v>
+      </c>
+      <c r="G20" t="s" s="9">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" t="s" s="9">
+        <v>51</v>
+      </c>
+      <c r="B21" t="s" s="9">
+        <v>52</v>
+      </c>
+      <c r="C21" s="10">
+        <v>2021</v>
+      </c>
+      <c r="D21" t="s" s="9">
+        <v>43</v>
+      </c>
+      <c r="E21" t="s" s="9">
+        <v>44</v>
+      </c>
+      <c r="F21" t="s" s="9">
+        <v>68</v>
+      </c>
+      <c r="G21" t="s" s="9">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" t="s" s="11">
+        <v>51</v>
+      </c>
+      <c r="B22" t="s" s="11">
+        <v>52</v>
+      </c>
+      <c r="C22" s="12">
+        <v>2021</v>
+      </c>
+      <c r="D22" t="s" s="11">
+        <v>43</v>
+      </c>
+      <c r="E22" t="s" s="11">
+        <v>44</v>
+      </c>
+      <c r="F22" t="s" s="11">
+        <v>70</v>
+      </c>
+      <c r="G22" t="s" s="11">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" t="s" s="11">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s" s="11">
+        <v>52</v>
+      </c>
+      <c r="C23" s="12">
+        <v>2021</v>
+      </c>
+      <c r="D23" t="s" s="11">
+        <v>43</v>
+      </c>
+      <c r="E23" t="s" s="11">
+        <v>44</v>
+      </c>
+      <c r="F23" t="s" s="11">
+        <v>70</v>
+      </c>
+      <c r="G23" t="s" s="11">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" t="s" s="11">
+        <v>51</v>
+      </c>
+      <c r="B24" t="s" s="11">
+        <v>52</v>
+      </c>
+      <c r="C24" s="12">
+        <v>2021</v>
+      </c>
+      <c r="D24" t="s" s="11">
+        <v>43</v>
+      </c>
+      <c r="E24" t="s" s="11">
+        <v>44</v>
+      </c>
+      <c r="F24" t="s" s="11">
+        <v>70</v>
+      </c>
+      <c r="G24" t="s" s="11">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" t="s" s="11">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s" s="11">
+        <v>75</v>
+      </c>
+      <c r="C25" s="12">
+        <v>2021</v>
+      </c>
+      <c r="D25" t="s" s="11">
+        <v>43</v>
+      </c>
+      <c r="E25" t="s" s="11">
+        <v>44</v>
+      </c>
+      <c r="F25" t="s" s="11">
+        <v>76</v>
+      </c>
+      <c r="G25" t="s" s="11">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" t="s" s="11">
+        <v>51</v>
+      </c>
+      <c r="B26" t="s" s="11">
+        <v>52</v>
+      </c>
+      <c r="C26" s="12">
+        <v>2022</v>
+      </c>
+      <c r="D26" t="s" s="11">
+        <v>43</v>
+      </c>
+      <c r="E26" t="s" s="11">
+        <v>44</v>
+      </c>
+      <c r="F26" t="s" s="11">
+        <v>70</v>
+      </c>
+      <c r="G26" t="s" s="11">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" t="s" s="13">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s" s="13">
+        <v>80</v>
+      </c>
+      <c r="C27" s="14">
+        <v>2021</v>
+      </c>
+      <c r="D27" t="s" s="13">
+        <v>81</v>
+      </c>
+      <c r="E27" t="s" s="13">
+        <v>82</v>
+      </c>
+      <c r="F27" t="s" s="13">
+        <v>83</v>
+      </c>
+      <c r="G27" t="s" s="13">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" t="s" s="13">
+        <v>79</v>
+      </c>
+      <c r="B28" t="s" s="13">
+        <v>80</v>
+      </c>
+      <c r="C28" s="14">
+        <v>2021</v>
+      </c>
+      <c r="D28" t="s" s="13">
+        <v>81</v>
+      </c>
+      <c r="E28" t="s" s="13">
+        <v>82</v>
+      </c>
+      <c r="F28" t="s" s="13">
+        <v>85</v>
+      </c>
+      <c r="G28" t="s" s="13">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" t="s" s="15">
+        <v>87</v>
+      </c>
+      <c r="B29" t="s" s="15">
+        <v>88</v>
+      </c>
+      <c r="C29" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D29" t="s" s="15">
+        <v>43</v>
+      </c>
+      <c r="E29" t="s" s="15">
+        <v>44</v>
+      </c>
+      <c r="F29" t="s" s="15">
+        <v>89</v>
+      </c>
+      <c r="G29" t="s" s="15">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" t="s" s="15">
+        <v>91</v>
+      </c>
+      <c r="B30" t="s" s="15">
+        <v>92</v>
+      </c>
+      <c r="C30" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D30" t="s" s="15">
+        <v>43</v>
+      </c>
+      <c r="E30" t="s" s="15">
+        <v>44</v>
+      </c>
+      <c r="F30" t="s" s="15">
+        <v>93</v>
+      </c>
+      <c r="G30" t="s" s="15">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" t="s" s="15">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s" s="15">
+        <v>95</v>
+      </c>
+      <c r="C31" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D31" t="s" s="15">
+        <v>43</v>
+      </c>
+      <c r="E31" t="s" s="15">
+        <v>44</v>
+      </c>
+      <c r="F31" t="s" s="15">
+        <v>32</v>
+      </c>
+      <c r="G31" t="s" s="15">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" t="s" s="15">
+        <v>97</v>
+      </c>
+      <c r="B32" t="s" s="15">
+        <v>98</v>
+      </c>
+      <c r="C32" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D32" t="s" s="15">
+        <v>43</v>
+      </c>
+      <c r="E32" t="s" s="15">
+        <v>44</v>
+      </c>
+      <c r="F32" t="s" s="15">
+        <v>99</v>
+      </c>
+      <c r="G32" t="s" s="15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" t="s" s="15">
+        <v>101</v>
+      </c>
+      <c r="B33" t="s" s="15">
+        <v>102</v>
+      </c>
+      <c r="C33" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D33" t="s" s="15">
+        <v>43</v>
+      </c>
+      <c r="E33" t="s" s="15">
+        <v>44</v>
+      </c>
+      <c r="F33" t="s" s="15">
+        <v>103</v>
+      </c>
+      <c r="G33" t="s" s="15">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" t="s" s="15">
+        <v>105</v>
+      </c>
+      <c r="B34" t="s" s="15">
+        <v>106</v>
+      </c>
+      <c r="C34" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D34" t="s" s="15">
+        <v>43</v>
+      </c>
+      <c r="E34" t="s" s="15">
+        <v>44</v>
+      </c>
+      <c r="F34" t="s" s="15">
+        <v>107</v>
+      </c>
+      <c r="G34" t="s" s="15">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" t="s" s="15">
+        <v>109</v>
+      </c>
+      <c r="B35" t="s" s="15">
+        <v>110</v>
+      </c>
+      <c r="C35" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D35" t="s" s="15">
+        <v>43</v>
+      </c>
+      <c r="E35" t="s" s="15">
+        <v>44</v>
+      </c>
+      <c r="F35" t="s" s="15">
+        <v>111</v>
+      </c>
+      <c r="G35" t="s" s="15">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" t="s" s="15">
+        <v>109</v>
+      </c>
+      <c r="B36" t="s" s="15">
+        <v>110</v>
+      </c>
+      <c r="C36" s="16">
+        <v>2023</v>
+      </c>
+      <c r="D36" t="s" s="15">
+        <v>43</v>
+      </c>
+      <c r="E36" t="s" s="15">
+        <v>44</v>
+      </c>
+      <c r="F36" t="s" s="15">
+        <v>113</v>
+      </c>
+      <c r="G36" t="s" s="15">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" t="s" s="17">
+        <v>91</v>
+      </c>
+      <c r="B37" t="s" s="17">
+        <v>115</v>
+      </c>
+      <c r="C37" s="18">
+        <v>2023</v>
+      </c>
+      <c r="D37" t="s" s="17">
+        <v>43</v>
+      </c>
+      <c r="E37" t="s" s="17">
+        <v>44</v>
+      </c>
+      <c r="F37" t="s" s="17">
+        <v>116</v>
+      </c>
+      <c r="G37" t="s" s="17">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" t="s" s="17">
+        <v>109</v>
+      </c>
+      <c r="B38" t="s" s="17">
+        <v>110</v>
+      </c>
+      <c r="C38" s="18">
+        <v>2023</v>
+      </c>
+      <c r="D38" t="s" s="17">
+        <v>43</v>
+      </c>
+      <c r="E38" t="s" s="17">
+        <v>44</v>
+      </c>
+      <c r="F38" t="s" s="17">
+        <v>118</v>
+      </c>
+      <c r="G38" t="s" s="17">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" t="s" s="17">
+        <v>109</v>
+      </c>
+      <c r="B39" t="s" s="17">
+        <v>110</v>
+      </c>
+      <c r="C39" s="18">
+        <v>2023</v>
+      </c>
+      <c r="D39" t="s" s="17">
+        <v>43</v>
+      </c>
+      <c r="E39" t="s" s="17">
+        <v>44</v>
+      </c>
+      <c r="F39" t="s" s="17">
+        <v>11</v>
+      </c>
+      <c r="G39" t="s" s="17">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" t="s" s="17">
+        <v>91</v>
+      </c>
+      <c r="B40" t="s" s="17">
+        <v>121</v>
+      </c>
+      <c r="C40" s="18">
+        <v>2024</v>
+      </c>
+      <c r="D40" t="s" s="17">
+        <v>43</v>
+      </c>
+      <c r="E40" t="s" s="17">
+        <v>44</v>
+      </c>
+      <c r="F40" t="s" s="17">
+        <v>122</v>
+      </c>
+      <c r="G40" t="s" s="17">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" t="s" s="17">
+        <v>124</v>
+      </c>
+      <c r="B41" t="s" s="17">
+        <v>125</v>
+      </c>
+      <c r="C41" s="18">
+        <v>2025</v>
+      </c>
+      <c r="D41" t="s" s="17">
+        <v>126</v>
+      </c>
+      <c r="E41" t="s" s="17">
+        <v>127</v>
+      </c>
+      <c r="F41" t="s" s="17">
+        <v>128</v>
+      </c>
+      <c r="G41" t="s" s="17">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="19"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="17"/>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="19"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/content/작품/작품리스트.xlsx
+++ b/content/작품/작품리스트.xlsx
@@ -256,10 +256,10 @@
     <t>Untitled-Ghost Print</t>
   </si>
   <si>
-    <t>모노타입</t>
-  </si>
-  <si>
-    <t>Monotype</t>
+    <t>종이 위에 모노타입</t>
+  </si>
+  <si>
+    <t>Monotype on paper</t>
   </si>
   <si>
     <t>50×65cm</t>
@@ -2601,48 +2601,48 @@
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" t="s" s="17">
+      <c r="A40" t="s" s="7">
         <v>91</v>
       </c>
-      <c r="B40" t="s" s="17">
+      <c r="B40" t="s" s="7">
         <v>121</v>
       </c>
-      <c r="C40" s="18">
+      <c r="C40" s="8">
         <v>2024</v>
       </c>
-      <c r="D40" t="s" s="17">
-        <v>43</v>
-      </c>
-      <c r="E40" t="s" s="17">
-        <v>44</v>
-      </c>
-      <c r="F40" t="s" s="17">
+      <c r="D40" t="s" s="7">
+        <v>43</v>
+      </c>
+      <c r="E40" t="s" s="7">
+        <v>44</v>
+      </c>
+      <c r="F40" t="s" s="7">
         <v>122</v>
       </c>
-      <c r="G40" t="s" s="17">
+      <c r="G40" t="s" s="7">
         <v>123</v>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" t="s" s="17">
+      <c r="A41" t="s" s="7">
         <v>124</v>
       </c>
-      <c r="B41" t="s" s="17">
+      <c r="B41" t="s" s="7">
         <v>125</v>
       </c>
-      <c r="C41" s="18">
+      <c r="C41" s="8">
         <v>2025</v>
       </c>
-      <c r="D41" t="s" s="17">
+      <c r="D41" t="s" s="7">
         <v>126</v>
       </c>
-      <c r="E41" t="s" s="17">
+      <c r="E41" t="s" s="7">
         <v>127</v>
       </c>
-      <c r="F41" t="s" s="17">
+      <c r="F41" t="s" s="7">
         <v>128</v>
       </c>
-      <c r="G41" t="s" s="17">
+      <c r="G41" t="s" s="7">
         <v>129</v>
       </c>
     </row>
